--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_encounters_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_encounters_SOURCE.xlsx
@@ -1386,7 +1386,7 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>1.669</v>
+        <v>1.668</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>1.641</v>
+        <v>1.642</v>
       </c>
       <c r="H26">
         <v>1.697</v>
@@ -1407,10 +1407,10 @@
         <v>1.641</v>
       </c>
       <c r="J26">
-        <v>1.697</v>
+        <v>1.698</v>
       </c>
       <c r="K26">
-        <v>1.641</v>
+        <v>1.64</v>
       </c>
       <c r="L26">
         <v>1.697</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>1.188</v>
+        <v>1.189</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1438,19 +1438,19 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>1.163</v>
+        <v>1.162</v>
       </c>
       <c r="H27">
-        <v>1.213</v>
+        <v>1.212</v>
       </c>
       <c r="I27">
-        <v>1.162</v>
+        <v>1.161</v>
       </c>
       <c r="J27">
-        <v>1.213</v>
+        <v>1.21</v>
       </c>
       <c r="K27">
-        <v>1.162</v>
+        <v>1.166</v>
       </c>
       <c r="L27">
         <v>1.214</v>
@@ -1481,13 +1481,13 @@
         <v>0.822</v>
       </c>
       <c r="H28">
-        <v>0.862</v>
+        <v>0.861</v>
       </c>
       <c r="I28">
-        <v>0.822</v>
+        <v>0.821</v>
       </c>
       <c r="J28">
-        <v>0.862</v>
+        <v>0.861</v>
       </c>
       <c r="K28">
         <v>0.822</v>
@@ -1512,25 +1512,25 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0.593</v>
+        <v>0.594</v>
       </c>
       <c r="H29">
-        <v>0.631</v>
+        <v>0.63</v>
       </c>
       <c r="I29">
         <v>0.594</v>
       </c>
       <c r="J29">
-        <v>0.631</v>
+        <v>0.629</v>
       </c>
       <c r="K29">
-        <v>0.593</v>
+        <v>0.595</v>
       </c>
       <c r="L29">
         <v>0.631</v>
@@ -1546,7 +1546,7 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>0.505</v>
+        <v>0.506</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1567,10 +1567,10 @@
         <v>0.489</v>
       </c>
       <c r="J30">
-        <v>0.523</v>
+        <v>0.522</v>
       </c>
       <c r="K30">
-        <v>0.489</v>
+        <v>0.49</v>
       </c>
       <c r="L30">
         <v>0.522</v>
@@ -1592,16 +1592,16 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0.408</v>
+        <v>0.409</v>
       </c>
       <c r="H31">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="I31">
         <v>0.408</v>
@@ -1638,19 +1638,19 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="H32">
-        <v>0.383</v>
+        <v>0.382</v>
       </c>
       <c r="I32">
         <v>0.355</v>
       </c>
       <c r="J32">
-        <v>0.383</v>
+        <v>0.382</v>
       </c>
       <c r="K32">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="L32">
         <v>0.382</v>
@@ -1684,16 +1684,16 @@
         <v>0.343</v>
       </c>
       <c r="I33">
-        <v>0.316</v>
+        <v>0.314</v>
       </c>
       <c r="J33">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="K33">
-        <v>0.315</v>
+        <v>0.317</v>
       </c>
       <c r="L33">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="34">
@@ -1724,13 +1724,13 @@
         <v>0.316</v>
       </c>
       <c r="I34">
-        <v>0.292</v>
+        <v>0.291</v>
       </c>
       <c r="J34">
         <v>0.316</v>
       </c>
       <c r="K34">
-        <v>0.291</v>
+        <v>0.29</v>
       </c>
       <c r="L34">
         <v>0.315</v>
@@ -1746,13 +1746,13 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>0.297</v>
+        <v>0.298</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1764,13 +1764,13 @@
         <v>0.311</v>
       </c>
       <c r="I35">
-        <v>0.285</v>
+        <v>0.286</v>
       </c>
       <c r="J35">
         <v>0.311</v>
       </c>
       <c r="K35">
-        <v>0.284</v>
+        <v>0.285</v>
       </c>
       <c r="L35">
         <v>0.31</v>
@@ -1807,10 +1807,10 @@
         <v>0.272</v>
       </c>
       <c r="J36">
-        <v>0.3</v>
+        <v>0.301</v>
       </c>
       <c r="K36">
-        <v>0.273</v>
+        <v>0.272</v>
       </c>
       <c r="L36">
         <v>0.301</v>
@@ -1826,7 +1826,7 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>0.302</v>
+        <v>0.303</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0.291</v>
+        <v>0.289</v>
       </c>
       <c r="H37">
-        <v>0.317</v>
+        <v>0.316</v>
       </c>
       <c r="I37">
-        <v>0.291</v>
+        <v>0.289</v>
       </c>
       <c r="J37">
         <v>0.317</v>
@@ -1853,7 +1853,7 @@
         <v>0.289</v>
       </c>
       <c r="L37">
-        <v>0.315</v>
+        <v>0.316</v>
       </c>
     </row>
     <row r="38">
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>0.254</v>
+        <v>0.255</v>
       </c>
       <c r="H38">
-        <v>0.279</v>
+        <v>0.278</v>
       </c>
       <c r="I38">
         <v>0.254</v>
       </c>
       <c r="J38">
-        <v>0.279</v>
+        <v>0.278</v>
       </c>
       <c r="K38">
         <v>0.254</v>
@@ -1927,10 +1927,10 @@
         <v>0.26</v>
       </c>
       <c r="J39">
-        <v>0.284</v>
+        <v>0.285</v>
       </c>
       <c r="K39">
-        <v>0.26</v>
+        <v>0.259</v>
       </c>
       <c r="L39">
         <v>0.285</v>
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1961,16 +1961,16 @@
         <v>0.254</v>
       </c>
       <c r="H40">
-        <v>0.28</v>
+        <v>0.279</v>
       </c>
       <c r="I40">
         <v>0.254</v>
       </c>
       <c r="J40">
-        <v>0.28</v>
+        <v>0.279</v>
       </c>
       <c r="K40">
-        <v>0.253</v>
+        <v>0.254</v>
       </c>
       <c r="L40">
         <v>0.279</v>
@@ -1986,13 +1986,13 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>0.274</v>
+        <v>0.275</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2001,19 +2001,19 @@
         <v>0.26</v>
       </c>
       <c r="H41">
-        <v>0.289</v>
+        <v>0.288</v>
       </c>
       <c r="I41">
-        <v>0.26</v>
+        <v>0.259</v>
       </c>
       <c r="J41">
-        <v>0.289</v>
+        <v>0.288</v>
       </c>
       <c r="K41">
-        <v>0.26</v>
+        <v>0.261</v>
       </c>
       <c r="L41">
-        <v>0.289</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="42">
@@ -2026,7 +2026,7 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>0.276</v>
+        <v>0.277</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>0.263</v>
       </c>
       <c r="J42">
-        <v>0.291</v>
+        <v>0.29</v>
       </c>
       <c r="K42">
-        <v>0.262</v>
+        <v>0.263</v>
       </c>
       <c r="L42">
-        <v>0.291</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="43">
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0.249</v>
+        <v>0.248</v>
       </c>
       <c r="H43">
         <v>0.276</v>
@@ -2106,22 +2106,22 @@
         <v>19</v>
       </c>
       <c r="C44">
-        <v>0.263</v>
+        <v>0.264</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44">
-        <v>0.249</v>
+        <v>0.25</v>
       </c>
       <c r="H44">
-        <v>0.279</v>
+        <v>0.278</v>
       </c>
       <c r="I44">
         <v>0.249</v>
@@ -2158,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>0.248</v>
+        <v>0.247</v>
       </c>
       <c r="H45">
         <v>0.275</v>
@@ -2167,10 +2167,10 @@
         <v>0.247</v>
       </c>
       <c r="J45">
-        <v>0.276</v>
+        <v>0.274</v>
       </c>
       <c r="K45">
-        <v>0.247</v>
+        <v>0.248</v>
       </c>
       <c r="L45">
         <v>0.275</v>
@@ -2186,7 +2186,7 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>0.266</v>
+        <v>0.267</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2201,19 +2201,19 @@
         <v>0.252</v>
       </c>
       <c r="H46">
+        <v>0.282</v>
+      </c>
+      <c r="I46">
+        <v>0.251</v>
+      </c>
+      <c r="J46">
+        <v>0.282</v>
+      </c>
+      <c r="K46">
+        <v>0.252</v>
+      </c>
+      <c r="L46">
         <v>0.283</v>
-      </c>
-      <c r="I46">
-        <v>0.252</v>
-      </c>
-      <c r="J46">
-        <v>0.283</v>
-      </c>
-      <c r="K46">
-        <v>0.251</v>
-      </c>
-      <c r="L46">
-        <v>0.282</v>
       </c>
     </row>
     <row r="47">
@@ -2244,7 +2244,7 @@
         <v>0.261</v>
       </c>
       <c r="I47">
-        <v>0.233</v>
+        <v>0.232</v>
       </c>
       <c r="J47">
         <v>0.261</v>
@@ -2266,7 +2266,7 @@
         <v>23</v>
       </c>
       <c r="C48">
-        <v>0.254</v>
+        <v>0.255</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2278,22 +2278,22 @@
         <v>0</v>
       </c>
       <c r="G48">
-        <v>0.239</v>
+        <v>0.238</v>
       </c>
       <c r="H48">
+        <v>0.27</v>
+      </c>
+      <c r="I48">
+        <v>0.238</v>
+      </c>
+      <c r="J48">
+        <v>0.269</v>
+      </c>
+      <c r="K48">
+        <v>0.24</v>
+      </c>
+      <c r="L48">
         <v>0.271</v>
-      </c>
-      <c r="I48">
-        <v>0.239</v>
-      </c>
-      <c r="J48">
-        <v>0.271</v>
-      </c>
-      <c r="K48">
-        <v>0.237</v>
-      </c>
-      <c r="L48">
-        <v>0.27</v>
       </c>
     </row>
     <row r="49">
@@ -2306,7 +2306,7 @@
         <v>24</v>
       </c>
       <c r="C49">
-        <v>0.241</v>
+        <v>0.242</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2318,13 +2318,13 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>0.228</v>
+        <v>0.227</v>
       </c>
       <c r="H49">
-        <v>0.256</v>
+        <v>0.255</v>
       </c>
       <c r="I49">
-        <v>0.228</v>
+        <v>0.226</v>
       </c>
       <c r="J49">
         <v>0.256</v>
@@ -2333,7 +2333,7 @@
         <v>0.227</v>
       </c>
       <c r="L49">
-        <v>0.255</v>
+        <v>0.257</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_encounters_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_encounters_SOURCE.xlsx
@@ -506,7 +506,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>0.764</v>
+        <v>0.724</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -518,22 +518,22 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.746</v>
+        <v>0.707</v>
       </c>
       <c r="H4">
-        <v>0.782</v>
+        <v>0.74</v>
       </c>
       <c r="I4">
-        <v>0.746</v>
+        <v>0.706</v>
       </c>
       <c r="J4">
-        <v>0.781</v>
+        <v>0.74</v>
       </c>
       <c r="K4">
-        <v>0.746</v>
+        <v>0.708</v>
       </c>
       <c r="L4">
-        <v>0.782</v>
+        <v>0.741</v>
       </c>
     </row>
     <row r="5">
@@ -546,7 +546,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>0.5600000000000001</v>
+        <v>0.507</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -558,22 +558,22 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.543</v>
+        <v>0.491</v>
       </c>
       <c r="H5">
-        <v>0.576</v>
+        <v>0.521</v>
       </c>
       <c r="I5">
-        <v>0.542</v>
+        <v>0.491</v>
       </c>
       <c r="J5">
-        <v>0.576</v>
+        <v>0.521</v>
       </c>
       <c r="K5">
-        <v>0.544</v>
+        <v>0.492</v>
       </c>
       <c r="L5">
-        <v>0.578</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="6">
@@ -586,34 +586,34 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>0.465</v>
+        <v>0.387</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.45</v>
+        <v>0.375</v>
       </c>
       <c r="H6">
-        <v>0.479</v>
+        <v>0.4</v>
       </c>
       <c r="I6">
-        <v>0.45</v>
+        <v>0.375</v>
       </c>
       <c r="J6">
-        <v>0.479</v>
+        <v>0.4</v>
       </c>
       <c r="K6">
-        <v>0.451</v>
+        <v>0.375</v>
       </c>
       <c r="L6">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7">
@@ -626,34 +626,34 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>0.39</v>
+        <v>0.308</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.377</v>
+        <v>0.298</v>
       </c>
       <c r="H7">
-        <v>0.404</v>
+        <v>0.319</v>
       </c>
       <c r="I7">
-        <v>0.377</v>
+        <v>0.298</v>
       </c>
       <c r="J7">
-        <v>0.404</v>
+        <v>0.319</v>
       </c>
       <c r="K7">
-        <v>0.377</v>
+        <v>0.298</v>
       </c>
       <c r="L7">
-        <v>0.403</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="8">
@@ -666,34 +666,34 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>0.341</v>
+        <v>0.258</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.328</v>
+        <v>0.248</v>
       </c>
       <c r="H8">
-        <v>0.354</v>
+        <v>0.269</v>
       </c>
       <c r="I8">
-        <v>0.327</v>
+        <v>0.248</v>
       </c>
       <c r="J8">
-        <v>0.354</v>
+        <v>0.269</v>
       </c>
       <c r="K8">
-        <v>0.328</v>
+        <v>0.248</v>
       </c>
       <c r="L8">
-        <v>0.354</v>
+        <v>0.269</v>
       </c>
     </row>
     <row r="9">
@@ -706,34 +706,34 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>0.306</v>
+        <v>0.223</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0.293</v>
+        <v>0.214</v>
       </c>
       <c r="H9">
-        <v>0.318</v>
+        <v>0.232</v>
       </c>
       <c r="I9">
-        <v>0.292</v>
+        <v>0.214</v>
       </c>
       <c r="J9">
-        <v>0.318</v>
+        <v>0.233</v>
       </c>
       <c r="K9">
-        <v>0.293</v>
+        <v>0.213</v>
       </c>
       <c r="L9">
-        <v>0.319</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="10">
@@ -746,34 +746,34 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>0.282</v>
+        <v>0.199</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.27</v>
+        <v>0.191</v>
       </c>
       <c r="H10">
-        <v>0.293</v>
+        <v>0.207</v>
       </c>
       <c r="I10">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="J10">
-        <v>0.293</v>
+        <v>0.207</v>
       </c>
       <c r="K10">
-        <v>0.27</v>
+        <v>0.191</v>
       </c>
       <c r="L10">
-        <v>0.294</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="11">
@@ -786,34 +786,34 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>0.277</v>
+        <v>0.19</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.265</v>
+        <v>0.181</v>
       </c>
       <c r="H11">
-        <v>0.289</v>
+        <v>0.198</v>
       </c>
       <c r="I11">
-        <v>0.264</v>
+        <v>0.18</v>
       </c>
       <c r="J11">
-        <v>0.288</v>
+        <v>0.198</v>
       </c>
       <c r="K11">
-        <v>0.266</v>
+        <v>0.181</v>
       </c>
       <c r="L11">
-        <v>0.29</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="12">
@@ -826,34 +826,34 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>0.267</v>
+        <v>0.176</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0.254</v>
+        <v>0.167</v>
       </c>
       <c r="H12">
-        <v>0.281</v>
+        <v>0.186</v>
       </c>
       <c r="I12">
-        <v>0.253</v>
+        <v>0.167</v>
       </c>
       <c r="J12">
-        <v>0.281</v>
+        <v>0.186</v>
       </c>
       <c r="K12">
-        <v>0.253</v>
+        <v>0.167</v>
       </c>
       <c r="L12">
-        <v>0.281</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="13">
@@ -866,34 +866,34 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>0.283</v>
+        <v>0.181</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.269</v>
+        <v>0.172</v>
       </c>
       <c r="H13">
-        <v>0.296</v>
+        <v>0.19</v>
       </c>
       <c r="I13">
-        <v>0.269</v>
+        <v>0.172</v>
       </c>
       <c r="J13">
-        <v>0.296</v>
+        <v>0.189</v>
       </c>
       <c r="K13">
-        <v>0.269</v>
+        <v>0.172</v>
       </c>
       <c r="L13">
-        <v>0.296</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="14">
@@ -906,34 +906,34 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>0.249</v>
+        <v>0.154</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0.237</v>
+        <v>0.147</v>
       </c>
       <c r="H14">
-        <v>0.26</v>
+        <v>0.161</v>
       </c>
       <c r="I14">
-        <v>0.237</v>
+        <v>0.147</v>
       </c>
       <c r="J14">
-        <v>0.26</v>
+        <v>0.161</v>
       </c>
       <c r="K14">
-        <v>0.238</v>
+        <v>0.147</v>
       </c>
       <c r="L14">
-        <v>0.26</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="15">
@@ -946,34 +946,34 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>0.255</v>
+        <v>0.153</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0.243</v>
+        <v>0.146</v>
       </c>
       <c r="H15">
-        <v>0.266</v>
+        <v>0.16</v>
       </c>
       <c r="I15">
-        <v>0.242</v>
+        <v>0.146</v>
       </c>
       <c r="J15">
-        <v>0.266</v>
+        <v>0.16</v>
       </c>
       <c r="K15">
-        <v>0.243</v>
+        <v>0.146</v>
       </c>
       <c r="L15">
-        <v>0.267</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="16">
@@ -986,34 +986,34 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>0.249</v>
+        <v>0.145</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0.237</v>
+        <v>0.138</v>
       </c>
       <c r="H16">
-        <v>0.262</v>
+        <v>0.153</v>
       </c>
       <c r="I16">
-        <v>0.235</v>
+        <v>0.137</v>
       </c>
       <c r="J16">
-        <v>0.261</v>
+        <v>0.152</v>
       </c>
       <c r="K16">
-        <v>0.237</v>
+        <v>0.138</v>
       </c>
       <c r="L16">
-        <v>0.263</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="17">
@@ -1026,34 +1026,34 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>0.257</v>
+        <v>0.145</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>0.243</v>
+        <v>0.137</v>
       </c>
       <c r="H17">
-        <v>0.271</v>
+        <v>0.153</v>
       </c>
       <c r="I17">
-        <v>0.242</v>
+        <v>0.137</v>
       </c>
       <c r="J17">
-        <v>0.27</v>
+        <v>0.152</v>
       </c>
       <c r="K17">
-        <v>0.244</v>
+        <v>0.138</v>
       </c>
       <c r="L17">
-        <v>0.272</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="18">
@@ -1066,34 +1066,34 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>0.259</v>
+        <v>0.141</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0.246</v>
+        <v>0.134</v>
       </c>
       <c r="H18">
-        <v>0.273</v>
+        <v>0.149</v>
       </c>
       <c r="I18">
-        <v>0.246</v>
+        <v>0.134</v>
       </c>
       <c r="J18">
-        <v>0.273</v>
+        <v>0.149</v>
       </c>
       <c r="K18">
-        <v>0.246</v>
+        <v>0.134</v>
       </c>
       <c r="L18">
-        <v>0.273</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="19">
@@ -1106,34 +1106,34 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>0.246</v>
+        <v>0.13</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0.233</v>
+        <v>0.123</v>
       </c>
       <c r="H19">
-        <v>0.259</v>
+        <v>0.137</v>
       </c>
       <c r="I19">
-        <v>0.233</v>
+        <v>0.123</v>
       </c>
       <c r="J19">
-        <v>0.259</v>
+        <v>0.137</v>
       </c>
       <c r="K19">
-        <v>0.233</v>
+        <v>0.123</v>
       </c>
       <c r="L19">
-        <v>0.259</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="20">
@@ -1146,34 +1146,34 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>0.247</v>
+        <v>0.127</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0.233</v>
+        <v>0.12</v>
       </c>
       <c r="H20">
-        <v>0.262</v>
+        <v>0.135</v>
       </c>
       <c r="I20">
-        <v>0.234</v>
+        <v>0.12</v>
       </c>
       <c r="J20">
-        <v>0.261</v>
+        <v>0.135</v>
       </c>
       <c r="K20">
-        <v>0.234</v>
+        <v>0.12</v>
       </c>
       <c r="L20">
-        <v>0.261</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="21">
@@ -1186,34 +1186,34 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>0.245</v>
+        <v>0.122</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0.232</v>
+        <v>0.116</v>
       </c>
       <c r="H21">
-        <v>0.258</v>
+        <v>0.129</v>
       </c>
       <c r="I21">
-        <v>0.232</v>
+        <v>0.115</v>
       </c>
       <c r="J21">
-        <v>0.258</v>
+        <v>0.129</v>
       </c>
       <c r="K21">
-        <v>0.232</v>
+        <v>0.116</v>
       </c>
       <c r="L21">
-        <v>0.259</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="22">
@@ -1226,34 +1226,34 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>0.25</v>
+        <v>0.121</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0.236</v>
+        <v>0.114</v>
       </c>
       <c r="H22">
-        <v>0.265</v>
+        <v>0.128</v>
       </c>
       <c r="I22">
-        <v>0.236</v>
+        <v>0.114</v>
       </c>
       <c r="J22">
-        <v>0.264</v>
+        <v>0.128</v>
       </c>
       <c r="K22">
-        <v>0.237</v>
+        <v>0.114</v>
       </c>
       <c r="L22">
-        <v>0.265</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="23">
@@ -1266,34 +1266,34 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>0.231</v>
+        <v>0.108</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0.218</v>
+        <v>0.102</v>
       </c>
       <c r="H23">
-        <v>0.245</v>
+        <v>0.115</v>
       </c>
       <c r="I23">
-        <v>0.218</v>
+        <v>0.101</v>
       </c>
       <c r="J23">
-        <v>0.244</v>
+        <v>0.114</v>
       </c>
       <c r="K23">
-        <v>0.218</v>
+        <v>0.102</v>
       </c>
       <c r="L23">
-        <v>0.244</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="24">
@@ -1306,34 +1306,34 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>0.239</v>
+        <v>0.108</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0.224</v>
+        <v>0.101</v>
       </c>
       <c r="H24">
-        <v>0.254</v>
+        <v>0.115</v>
       </c>
       <c r="I24">
-        <v>0.224</v>
+        <v>0.101</v>
       </c>
       <c r="J24">
-        <v>0.253</v>
+        <v>0.115</v>
       </c>
       <c r="K24">
-        <v>0.225</v>
+        <v>0.101</v>
       </c>
       <c r="L24">
-        <v>0.254</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="25">
@@ -1346,34 +1346,34 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>0.227</v>
+        <v>0.099</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0.213</v>
+        <v>0.093</v>
       </c>
       <c r="H25">
-        <v>0.24</v>
+        <v>0.105</v>
       </c>
       <c r="I25">
-        <v>0.213</v>
+        <v>0.093</v>
       </c>
       <c r="J25">
-        <v>0.24</v>
+        <v>0.105</v>
       </c>
       <c r="K25">
-        <v>0.214</v>
+        <v>0.094</v>
       </c>
       <c r="L25">
-        <v>0.241</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="26">
@@ -1466,7 +1466,7 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>0.842</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1478,22 +1478,22 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.822</v>
+        <v>0.789</v>
       </c>
       <c r="H28">
-        <v>0.861</v>
+        <v>0.827</v>
       </c>
       <c r="I28">
-        <v>0.821</v>
+        <v>0.789</v>
       </c>
       <c r="J28">
-        <v>0.861</v>
+        <v>0.827</v>
       </c>
       <c r="K28">
-        <v>0.822</v>
+        <v>0.79</v>
       </c>
       <c r="L28">
-        <v>0.862</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="29">
@@ -1506,34 +1506,34 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>0.612</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0.594</v>
+        <v>0.549</v>
       </c>
       <c r="H29">
-        <v>0.63</v>
+        <v>0.582</v>
       </c>
       <c r="I29">
-        <v>0.594</v>
+        <v>0.548</v>
       </c>
       <c r="J29">
-        <v>0.629</v>
+        <v>0.582</v>
       </c>
       <c r="K29">
-        <v>0.595</v>
+        <v>0.549</v>
       </c>
       <c r="L29">
-        <v>0.631</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="30">
@@ -1546,34 +1546,34 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>0.506</v>
+        <v>0.433</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0.49</v>
+        <v>0.418</v>
       </c>
       <c r="H30">
-        <v>0.522</v>
+        <v>0.447</v>
       </c>
       <c r="I30">
-        <v>0.489</v>
+        <v>0.418</v>
       </c>
       <c r="J30">
-        <v>0.522</v>
+        <v>0.446</v>
       </c>
       <c r="K30">
-        <v>0.49</v>
+        <v>0.419</v>
       </c>
       <c r="L30">
-        <v>0.522</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="31">
@@ -1586,34 +1586,34 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.422</v>
+        <v>0.344</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0.409</v>
+        <v>0.333</v>
       </c>
       <c r="H31">
-        <v>0.437</v>
+        <v>0.357</v>
       </c>
       <c r="I31">
-        <v>0.408</v>
+        <v>0.333</v>
       </c>
       <c r="J31">
-        <v>0.437</v>
+        <v>0.357</v>
       </c>
       <c r="K31">
-        <v>0.408</v>
+        <v>0.332</v>
       </c>
       <c r="L31">
-        <v>0.437</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="32">
@@ -1626,34 +1626,34 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>0.368</v>
+        <v>0.288</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0.355</v>
+        <v>0.278</v>
       </c>
       <c r="H32">
-        <v>0.382</v>
+        <v>0.3</v>
       </c>
       <c r="I32">
-        <v>0.355</v>
+        <v>0.278</v>
       </c>
       <c r="J32">
-        <v>0.382</v>
+        <v>0.299</v>
       </c>
       <c r="K32">
-        <v>0.355</v>
+        <v>0.278</v>
       </c>
       <c r="L32">
-        <v>0.382</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33">
@@ -1666,34 +1666,34 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>0.329</v>
+        <v>0.249</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>0.316</v>
+        <v>0.239</v>
       </c>
       <c r="H33">
-        <v>0.343</v>
+        <v>0.26</v>
       </c>
       <c r="I33">
-        <v>0.314</v>
+        <v>0.238</v>
       </c>
       <c r="J33">
-        <v>0.342</v>
+        <v>0.259</v>
       </c>
       <c r="K33">
-        <v>0.317</v>
+        <v>0.239</v>
       </c>
       <c r="L33">
-        <v>0.344</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="34">
@@ -1706,34 +1706,34 @@
         <v>9</v>
       </c>
       <c r="C34">
-        <v>0.303</v>
+        <v>0.222</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>0.291</v>
+        <v>0.212</v>
       </c>
       <c r="H34">
-        <v>0.316</v>
+        <v>0.231</v>
       </c>
       <c r="I34">
-        <v>0.291</v>
+        <v>0.212</v>
       </c>
       <c r="J34">
-        <v>0.316</v>
+        <v>0.232</v>
       </c>
       <c r="K34">
-        <v>0.29</v>
+        <v>0.212</v>
       </c>
       <c r="L34">
-        <v>0.315</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="35">
@@ -1746,34 +1746,34 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>0.298</v>
+        <v>0.212</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0.285</v>
+        <v>0.202</v>
       </c>
       <c r="H35">
-        <v>0.311</v>
+        <v>0.221</v>
       </c>
       <c r="I35">
-        <v>0.286</v>
+        <v>0.202</v>
       </c>
       <c r="J35">
-        <v>0.311</v>
+        <v>0.221</v>
       </c>
       <c r="K35">
-        <v>0.285</v>
+        <v>0.202</v>
       </c>
       <c r="L35">
-        <v>0.31</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="36">
@@ -1786,34 +1786,34 @@
         <v>11</v>
       </c>
       <c r="C36">
-        <v>0.286</v>
+        <v>0.197</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="F36">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0.273</v>
+        <v>0.187</v>
       </c>
       <c r="H36">
-        <v>0.301</v>
+        <v>0.207</v>
       </c>
       <c r="I36">
-        <v>0.272</v>
+        <v>0.187</v>
       </c>
       <c r="J36">
-        <v>0.301</v>
+        <v>0.207</v>
       </c>
       <c r="K36">
-        <v>0.272</v>
+        <v>0.187</v>
       </c>
       <c r="L36">
-        <v>0.301</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="37">
@@ -1826,34 +1826,34 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>0.303</v>
+        <v>0.202</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="F37">
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0.289</v>
+        <v>0.193</v>
       </c>
       <c r="H37">
-        <v>0.316</v>
+        <v>0.211</v>
       </c>
       <c r="I37">
-        <v>0.289</v>
+        <v>0.193</v>
       </c>
       <c r="J37">
-        <v>0.317</v>
+        <v>0.211</v>
       </c>
       <c r="K37">
-        <v>0.289</v>
+        <v>0.193</v>
       </c>
       <c r="L37">
-        <v>0.316</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="38">
@@ -1866,34 +1866,34 @@
         <v>13</v>
       </c>
       <c r="C38">
-        <v>0.266</v>
+        <v>0.172</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>0.255</v>
+        <v>0.164</v>
       </c>
       <c r="H38">
-        <v>0.278</v>
+        <v>0.18</v>
       </c>
       <c r="I38">
-        <v>0.254</v>
+        <v>0.164</v>
       </c>
       <c r="J38">
-        <v>0.278</v>
+        <v>0.18</v>
       </c>
       <c r="K38">
-        <v>0.254</v>
+        <v>0.164</v>
       </c>
       <c r="L38">
-        <v>0.278</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="39">
@@ -1906,34 +1906,34 @@
         <v>14</v>
       </c>
       <c r="C39">
-        <v>0.272</v>
+        <v>0.171</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>0.26</v>
+        <v>0.163</v>
       </c>
       <c r="H39">
-        <v>0.285</v>
+        <v>0.179</v>
       </c>
       <c r="I39">
-        <v>0.26</v>
+        <v>0.162</v>
       </c>
       <c r="J39">
-        <v>0.285</v>
+        <v>0.179</v>
       </c>
       <c r="K39">
-        <v>0.259</v>
+        <v>0.162</v>
       </c>
       <c r="L39">
-        <v>0.285</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="40">
@@ -1946,34 +1946,34 @@
         <v>15</v>
       </c>
       <c r="C40">
-        <v>0.266</v>
+        <v>0.162</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40">
-        <v>0.254</v>
+        <v>0.154</v>
       </c>
       <c r="H40">
-        <v>0.279</v>
+        <v>0.17</v>
       </c>
       <c r="I40">
-        <v>0.254</v>
+        <v>0.154</v>
       </c>
       <c r="J40">
-        <v>0.279</v>
+        <v>0.17</v>
       </c>
       <c r="K40">
-        <v>0.254</v>
+        <v>0.154</v>
       </c>
       <c r="L40">
-        <v>0.279</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="41">
@@ -1986,34 +1986,34 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>0.275</v>
+        <v>0.162</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0.26</v>
+        <v>0.153</v>
       </c>
       <c r="H41">
-        <v>0.288</v>
+        <v>0.17</v>
       </c>
       <c r="I41">
-        <v>0.259</v>
+        <v>0.153</v>
       </c>
       <c r="J41">
-        <v>0.288</v>
+        <v>0.17</v>
       </c>
       <c r="K41">
-        <v>0.261</v>
+        <v>0.154</v>
       </c>
       <c r="L41">
-        <v>0.29</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="42">
@@ -2026,34 +2026,34 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>0.277</v>
+        <v>0.158</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42">
-        <v>0.263</v>
+        <v>0.15</v>
       </c>
       <c r="H42">
-        <v>0.291</v>
+        <v>0.166</v>
       </c>
       <c r="I42">
-        <v>0.263</v>
+        <v>0.15</v>
       </c>
       <c r="J42">
-        <v>0.29</v>
+        <v>0.166</v>
       </c>
       <c r="K42">
-        <v>0.263</v>
+        <v>0.15</v>
       </c>
       <c r="L42">
-        <v>0.29</v>
+        <v>0.166</v>
       </c>
     </row>
     <row r="43">
@@ -2066,34 +2066,34 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>0.262</v>
+        <v>0.146</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0.248</v>
+        <v>0.138</v>
       </c>
       <c r="H43">
-        <v>0.276</v>
+        <v>0.153</v>
       </c>
       <c r="I43">
-        <v>0.249</v>
+        <v>0.137</v>
       </c>
       <c r="J43">
-        <v>0.276</v>
+        <v>0.153</v>
       </c>
       <c r="K43">
-        <v>0.249</v>
+        <v>0.138</v>
       </c>
       <c r="L43">
-        <v>0.276</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="44">
@@ -2106,34 +2106,34 @@
         <v>19</v>
       </c>
       <c r="C44">
-        <v>0.264</v>
+        <v>0.142</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44">
-        <v>0.25</v>
+        <v>0.134</v>
       </c>
       <c r="H44">
-        <v>0.278</v>
+        <v>0.15</v>
       </c>
       <c r="I44">
-        <v>0.249</v>
+        <v>0.134</v>
       </c>
       <c r="J44">
-        <v>0.279</v>
+        <v>0.15</v>
       </c>
       <c r="K44">
-        <v>0.249</v>
+        <v>0.134</v>
       </c>
       <c r="L44">
-        <v>0.279</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="45">
@@ -2146,34 +2146,34 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>0.261</v>
+        <v>0.137</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45">
-        <v>0.247</v>
+        <v>0.129</v>
       </c>
       <c r="H45">
-        <v>0.275</v>
+        <v>0.144</v>
       </c>
       <c r="I45">
-        <v>0.247</v>
+        <v>0.129</v>
       </c>
       <c r="J45">
-        <v>0.274</v>
+        <v>0.144</v>
       </c>
       <c r="K45">
-        <v>0.248</v>
+        <v>0.129</v>
       </c>
       <c r="L45">
-        <v>0.275</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="46">
@@ -2186,34 +2186,34 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>0.267</v>
+        <v>0.135</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="F46">
         <v>0</v>
       </c>
       <c r="G46">
-        <v>0.252</v>
+        <v>0.127</v>
       </c>
       <c r="H46">
-        <v>0.282</v>
+        <v>0.143</v>
       </c>
       <c r="I46">
-        <v>0.251</v>
+        <v>0.127</v>
       </c>
       <c r="J46">
-        <v>0.282</v>
+        <v>0.143</v>
       </c>
       <c r="K46">
-        <v>0.252</v>
+        <v>0.128</v>
       </c>
       <c r="L46">
-        <v>0.283</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="47">
@@ -2226,34 +2226,34 @@
         <v>22</v>
       </c>
       <c r="C47">
-        <v>0.246</v>
+        <v>0.121</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47">
-        <v>0.232</v>
+        <v>0.114</v>
       </c>
       <c r="H47">
-        <v>0.261</v>
+        <v>0.128</v>
       </c>
       <c r="I47">
-        <v>0.232</v>
+        <v>0.114</v>
       </c>
       <c r="J47">
-        <v>0.261</v>
+        <v>0.128</v>
       </c>
       <c r="K47">
-        <v>0.232</v>
+        <v>0.114</v>
       </c>
       <c r="L47">
-        <v>0.26</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="48">
@@ -2266,34 +2266,34 @@
         <v>23</v>
       </c>
       <c r="C48">
-        <v>0.255</v>
+        <v>0.121</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48">
-        <v>0.238</v>
+        <v>0.113</v>
       </c>
       <c r="H48">
-        <v>0.27</v>
+        <v>0.128</v>
       </c>
       <c r="I48">
-        <v>0.238</v>
+        <v>0.112</v>
       </c>
       <c r="J48">
-        <v>0.269</v>
+        <v>0.128</v>
       </c>
       <c r="K48">
-        <v>0.24</v>
+        <v>0.114</v>
       </c>
       <c r="L48">
-        <v>0.271</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="49">
@@ -2306,34 +2306,34 @@
         <v>24</v>
       </c>
       <c r="C49">
-        <v>0.242</v>
+        <v>0.111</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
       <c r="G49">
-        <v>0.227</v>
+        <v>0.104</v>
       </c>
       <c r="H49">
-        <v>0.255</v>
+        <v>0.118</v>
       </c>
       <c r="I49">
-        <v>0.226</v>
+        <v>0.103</v>
       </c>
       <c r="J49">
-        <v>0.256</v>
+        <v>0.118</v>
       </c>
       <c r="K49">
-        <v>0.227</v>
+        <v>0.104</v>
       </c>
       <c r="L49">
-        <v>0.257</v>
+        <v>0.119</v>
       </c>
     </row>
   </sheetData>
